--- a/data/nbb.xlsx
+++ b/data/nbb.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\dm\DM Office\Secrétariat des protocoles\Changes\2025\2025-08-04\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\nbb.local\res\Library\PRXNWEBP\DOC\BE\BE\protocol\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6F25C1C5-47F2-48AA-9C22-0D51C027E7C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FE09956-C2C9-4D76-89CD-2465F76ED514}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22275" yWindow="3300" windowWidth="41355" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2685" yWindow="2685" windowWidth="28800" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Q_06B_Link_Created_Groups_to_Na" sheetId="1" r:id="rId1"/>
@@ -844,7 +844,7 @@
     <t>BMPB BE BB</t>
   </si>
   <si>
-    <t>Aion</t>
+    <t>UniCredit SA/NV</t>
   </si>
   <si>
     <t>644</t>
@@ -1825,7 +1825,7 @@
     <t>Numéros réservés aux paiements par chèques circulaires et assignations</t>
   </si>
   <si>
-    <t>Version 04/08/2025</t>
+    <t>Version 06/10/2025</t>
   </si>
 </sst>
 </file>
@@ -8547,6 +8547,14 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 NBB - Public</oddFooter>
+  </headerFooter>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{3f6fa8f2-45b3-4617-b6ca-bd4433a2a147}" enabled="1" method="Privileged" siteId="{43f10d24-b9bf-46da-a9c8-15c1b0990ce7}" contentBits="2" removed="0"/>
+</clbl:labelList>
 </file>